--- a/artfynd/Maskaure Siebdniesjávrrie-Lillberget, 122 ha artfynd.xlsx
+++ b/artfynd/Maskaure Siebdniesjávrrie-Lillberget, 122 ha artfynd.xlsx
@@ -9560,12 +9560,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Agne Jonsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Agne Jonsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">

--- a/artfynd/Maskaure Siebdniesjávrrie-Lillberget, 122 ha artfynd.xlsx
+++ b/artfynd/Maskaure Siebdniesjávrrie-Lillberget, 122 ha artfynd.xlsx
@@ -8020,7 +8020,7 @@
         <v>0</v>
       </c>
       <c r="AE65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG65" t="b">
         <v>0</v>

--- a/artfynd/Maskaure Siebdniesjávrrie-Lillberget, 122 ha artfynd.xlsx
+++ b/artfynd/Maskaure Siebdniesjávrrie-Lillberget, 122 ha artfynd.xlsx
@@ -12583,7 +12583,7 @@
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand, Anton Lundberg</t>
+          <t>Anton Lundberg, Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">

--- a/artfynd/Maskaure Siebdniesjávrrie-Lillberget, 122 ha artfynd.xlsx
+++ b/artfynd/Maskaure Siebdniesjávrrie-Lillberget, 122 ha artfynd.xlsx
@@ -12583,7 +12583,7 @@
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Anton Lundberg, Alva Dahlqvist Cederstrand</t>
+          <t>Alva Dahlqvist Cederstrand, Anton Lundberg</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">

--- a/artfynd/Maskaure Siebdniesjávrrie-Lillberget, 122 ha artfynd.xlsx
+++ b/artfynd/Maskaure Siebdniesjávrrie-Lillberget, 122 ha artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY186"/>
+  <dimension ref="A1:AZ186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323678</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379336</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1015,6 +1030,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323656</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1126,6 +1146,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323657</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1247,6 +1272,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321655</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1381,6 +1411,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323677</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1505,6 +1540,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325373</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1624,6 +1664,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323086</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1740,6 +1785,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321654</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1851,6 +1901,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323087</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1962,6 +2017,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325359</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2073,6 +2133,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325368</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2184,6 +2249,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379319</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2295,6 +2365,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325365</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2406,6 +2481,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323653</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2517,6 +2597,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325357</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2628,6 +2713,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325364</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2739,6 +2829,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379316</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2850,6 +2945,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379331</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2961,6 +3061,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379317</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3072,6 +3177,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379320</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3193,6 +3303,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323652</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3304,6 +3419,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325354</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3415,6 +3535,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325356</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3526,6 +3651,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325369</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3637,6 +3767,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379315</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3748,6 +3883,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379335</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3859,6 +3999,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379330</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3970,6 +4115,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379322</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4081,6 +4231,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325370</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4192,6 +4347,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321631</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4303,6 +4463,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321634</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4414,6 +4579,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321636</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4525,6 +4695,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321640</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4636,6 +4811,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321650</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4762,6 +4942,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323672</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4881,6 +5066,11 @@
       <c r="AY38" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323673</t>
         </is>
       </c>
     </row>
@@ -4998,6 +5188,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326033</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5109,6 +5304,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379323</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5220,6 +5420,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379334</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5331,6 +5536,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321635</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5442,6 +5652,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321645</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5553,6 +5768,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321646</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5664,6 +5884,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321651</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5775,6 +6000,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379321</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5886,6 +6116,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379324</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5997,6 +6232,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379327</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6108,6 +6348,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379333</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6219,6 +6464,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379318</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6340,6 +6590,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321632</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6461,6 +6716,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321638</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6577,6 +6837,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321641</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6698,6 +6963,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321642</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6819,6 +7089,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321643</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6940,6 +7215,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321647</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7061,6 +7341,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321648</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7182,6 +7467,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321649</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7303,6 +7593,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321652</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7424,6 +7719,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321653</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7545,6 +7845,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323670</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7669,6 +7974,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323675</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7793,6 +8103,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323676</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7917,6 +8232,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325355</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8041,6 +8361,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325358</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8165,6 +8490,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325360</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8289,6 +8619,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325361</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8413,6 +8748,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325363</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8537,6 +8877,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325372</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8653,6 +8998,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379329</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8764,6 +9114,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379332</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8888,6 +9243,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323083</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -9007,6 +9367,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325353</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9118,6 +9483,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323655</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9234,6 +9604,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321637</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9345,6 +9720,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323085</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9456,6 +9836,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379325</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9571,6 +9956,11 @@
       <c r="AY78" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135324140</t>
         </is>
       </c>
     </row>
@@ -9693,6 +10083,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326029</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9804,6 +10199,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379341</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9915,6 +10315,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379342</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -10021,6 +10426,11 @@
           <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7175049</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -10123,6 +10533,11 @@
           <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7175050</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10220,6 +10635,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95999773</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10331,6 +10751,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323088</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10428,6 +10853,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96001582</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10539,6 +10969,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321659</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10650,6 +11085,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321666</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10761,6 +11201,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323658</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10872,6 +11317,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379339</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10983,6 +11433,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379340</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -11094,6 +11549,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321660</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -11205,6 +11665,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321668</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11302,6 +11767,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96001584</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11413,6 +11883,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321663</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11524,6 +11999,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321665</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11635,6 +12115,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325374</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11746,6 +12231,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325376</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11867,6 +12357,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321671</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11988,6 +12483,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321672</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -12112,6 +12612,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323090</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -12231,6 +12736,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323092</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12347,6 +12857,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325377</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12469,6 +12984,11 @@
       <c r="AY104" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325378</t>
         </is>
       </c>
     </row>
@@ -12591,6 +13111,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326036</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12707,6 +13232,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321667</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12823,6 +13353,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321669</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12934,6 +13469,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321658</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -13031,6 +13571,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96001585</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -13142,6 +13687,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323095</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -13258,6 +13808,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321662</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -13374,6 +13929,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321664</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13490,6 +14050,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321670</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13601,6 +14166,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323089</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13712,6 +14282,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323093</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13814,6 +14389,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96001579</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13925,6 +14505,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325384</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -14022,6 +14607,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96001591</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -14119,6 +14709,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95999776</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -14216,6 +14811,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96001561</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -14313,6 +14913,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96001574</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -14410,6 +15015,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96001575</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -14507,6 +15117,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96001590</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14604,6 +15219,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96001603</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14701,6 +15321,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96001592</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14798,6 +15423,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96001600</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14895,6 +15525,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96001526</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14992,6 +15627,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96001577</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -15089,6 +15729,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96001589</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -15186,6 +15831,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96001601</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -15283,6 +15933,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96001520</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -15394,6 +16049,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325383</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -15491,6 +16151,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96001527</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15588,6 +16253,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91822633</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15685,6 +16355,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95999780</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15782,6 +16457,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95999781</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -15879,6 +16559,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96001524</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -15976,6 +16661,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96001525</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -16073,6 +16763,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96001594</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -16170,6 +16865,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96001595</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -16267,6 +16967,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96001596</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -16364,6 +17069,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96001528</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -16461,6 +17171,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96001510</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -16558,6 +17273,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96001511</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -16655,6 +17375,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96001576</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -16752,6 +17477,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96001586</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -16858,6 +17588,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7123094</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -16964,6 +17699,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7123110</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -17061,6 +17801,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96001512</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -17158,6 +17903,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96001513</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -17255,6 +18005,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96001560</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -17366,6 +18121,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321675</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -17477,6 +18237,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325385</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -17574,6 +18339,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95999775</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -17671,6 +18441,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95999782</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -17777,6 +18552,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96001509</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -17883,6 +18663,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96001588</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -18003,6 +18788,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326030</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -18100,6 +18890,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96001514</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -18219,6 +19014,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321676</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -18325,6 +19125,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96001558</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -18422,6 +19227,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96001517</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -18523,6 +19333,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96001593</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -18620,6 +19435,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96001598</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -18717,6 +19537,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96001518</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -18814,6 +19639,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96001519</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -18911,6 +19741,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96001516</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -19008,6 +19843,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91822628</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -19105,6 +19945,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95999774</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -19202,6 +20047,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96001564</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -19299,6 +20149,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96001553</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -19425,6 +20280,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321674</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -19536,6 +20396,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325382</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -19633,6 +20498,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91822596</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -19730,6 +20600,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96001562</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -19841,6 +20716,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379346</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -19938,6 +20818,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96001551</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -20049,6 +20934,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321673</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -20160,6 +21050,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379343</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -20282,6 +21177,11 @@
       <c r="AY180" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325381</t>
         </is>
       </c>
     </row>
@@ -20404,6 +21304,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326032</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -20510,6 +21415,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96001550</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -20607,6 +21517,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96001565</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -20727,6 +21642,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325379</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -20838,6 +21758,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379344</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -20949,8 +21874,200 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379345</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/Maskaure Siebdniesjávrrie-Lillberget, 122 ha artfynd.xlsx
+++ b/artfynd/Maskaure Siebdniesjávrrie-Lillberget, 122 ha artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135323678</v>
       </c>
       <c r="B2" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>135379336</v>
       </c>
       <c r="B3" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>135323656</v>
       </c>
       <c r="B4" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>135323657</v>
       </c>
       <c r="B5" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>135321655</v>
       </c>
       <c r="B6" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>135323677</v>
       </c>
       <c r="B7" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>135325373</v>
       </c>
       <c r="B8" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>135323086</v>
       </c>
       <c r="B9" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>135321654</v>
       </c>
       <c r="B10" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>135323087</v>
       </c>
       <c r="B11" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>135325359</v>
       </c>
       <c r="B12" t="n">
-        <v>91924</v>
+        <v>91966</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>135325368</v>
       </c>
       <c r="B13" t="n">
-        <v>91924</v>
+        <v>91966</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>135379319</v>
       </c>
       <c r="B14" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>135325365</v>
       </c>
       <c r="B15" t="n">
-        <v>89354</v>
+        <v>89396</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>135323653</v>
       </c>
       <c r="B16" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>135325357</v>
       </c>
       <c r="B17" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>135325364</v>
       </c>
       <c r="B18" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>135379316</v>
       </c>
       <c r="B19" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>135379331</v>
       </c>
       <c r="B20" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         <v>135379317</v>
       </c>
       <c r="B21" t="n">
-        <v>81355</v>
+        <v>81393</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>135379320</v>
       </c>
       <c r="B22" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         <v>135323652</v>
       </c>
       <c r="B23" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>135325354</v>
       </c>
       <c r="B24" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>135325356</v>
       </c>
       <c r="B25" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>135325369</v>
       </c>
       <c r="B26" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>135379315</v>
       </c>
       <c r="B27" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
         <v>135379335</v>
       </c>
       <c r="B28" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>135379330</v>
       </c>
       <c r="B29" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>135379322</v>
       </c>
       <c r="B30" t="n">
-        <v>92329</v>
+        <v>92371</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>135325370</v>
       </c>
       <c r="B31" t="n">
-        <v>92320</v>
+        <v>92362</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>135321631</v>
       </c>
       <c r="B32" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>135321634</v>
       </c>
       <c r="B33" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         <v>135321636</v>
       </c>
       <c r="B34" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>135321640</v>
       </c>
       <c r="B35" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>135321650</v>
       </c>
       <c r="B36" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>135323672</v>
       </c>
       <c r="B37" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
         <v>135323673</v>
       </c>
       <c r="B38" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>135326033</v>
       </c>
       <c r="B39" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>135379323</v>
       </c>
       <c r="B40" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5315,7 +5315,7 @@
         <v>135379334</v>
       </c>
       <c r="B41" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         <v>135321635</v>
       </c>
       <c r="B42" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5547,7 +5547,7 @@
         <v>135321645</v>
       </c>
       <c r="B43" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
         <v>135321646</v>
       </c>
       <c r="B44" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5779,7 +5779,7 @@
         <v>135321651</v>
       </c>
       <c r="B45" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5895,7 +5895,7 @@
         <v>135379321</v>
       </c>
       <c r="B46" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6011,7 +6011,7 @@
         <v>135379324</v>
       </c>
       <c r="B47" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         <v>135379327</v>
       </c>
       <c r="B48" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6243,7 +6243,7 @@
         <v>135379333</v>
       </c>
       <c r="B49" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         <v>135379318</v>
       </c>
       <c r="B50" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6475,7 +6475,7 @@
         <v>135321632</v>
       </c>
       <c r="B51" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
         <v>135321638</v>
       </c>
       <c r="B52" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         <v>135321641</v>
       </c>
       <c r="B53" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>135321642</v>
       </c>
       <c r="B54" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
         <v>135321643</v>
       </c>
       <c r="B55" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7100,7 +7100,7 @@
         <v>135321647</v>
       </c>
       <c r="B56" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7226,7 +7226,7 @@
         <v>135321648</v>
       </c>
       <c r="B57" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7352,7 +7352,7 @@
         <v>135321649</v>
       </c>
       <c r="B58" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7478,7 +7478,7 @@
         <v>135321652</v>
       </c>
       <c r="B59" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7604,7 +7604,7 @@
         <v>135321653</v>
       </c>
       <c r="B60" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7730,7 +7730,7 @@
         <v>135323670</v>
       </c>
       <c r="B61" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         <v>135323675</v>
       </c>
       <c r="B62" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7985,7 +7985,7 @@
         <v>135323676</v>
       </c>
       <c r="B63" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         <v>135325355</v>
       </c>
       <c r="B64" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8243,7 +8243,7 @@
         <v>135325358</v>
       </c>
       <c r="B65" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
         <v>135325360</v>
       </c>
       <c r="B66" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8501,7 +8501,7 @@
         <v>135325361</v>
       </c>
       <c r="B67" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8630,7 +8630,7 @@
         <v>135325363</v>
       </c>
       <c r="B68" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8759,7 +8759,7 @@
         <v>135325372</v>
       </c>
       <c r="B69" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8888,7 +8888,7 @@
         <v>135379329</v>
       </c>
       <c r="B70" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9009,7 +9009,7 @@
         <v>135379332</v>
       </c>
       <c r="B71" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9125,7 +9125,7 @@
         <v>135323083</v>
       </c>
       <c r="B72" t="n">
-        <v>57165</v>
+        <v>57170</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>135325353</v>
       </c>
       <c r="B73" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9494,7 +9494,7 @@
         <v>135321637</v>
       </c>
       <c r="B75" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9615,7 +9615,7 @@
         <v>135323085</v>
       </c>
       <c r="B76" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9731,7 +9731,7 @@
         <v>135379325</v>
       </c>
       <c r="B77" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9847,7 +9847,7 @@
         <v>135324140</v>
       </c>
       <c r="B78" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         <v>135326029</v>
       </c>
       <c r="B79" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10094,7 +10094,7 @@
         <v>135379341</v>
       </c>
       <c r="B80" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10210,7 +10210,7 @@
         <v>135379342</v>
       </c>
       <c r="B81" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10646,7 +10646,7 @@
         <v>135323088</v>
       </c>
       <c r="B85" t="n">
-        <v>97308</v>
+        <v>97352</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10864,7 +10864,7 @@
         <v>135321659</v>
       </c>
       <c r="B87" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
         <v>135321666</v>
       </c>
       <c r="B88" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11096,7 +11096,7 @@
         <v>135323658</v>
       </c>
       <c r="B89" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11212,7 +11212,7 @@
         <v>135379339</v>
       </c>
       <c r="B90" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11328,7 +11328,7 @@
         <v>135379340</v>
       </c>
       <c r="B91" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11444,7 +11444,7 @@
         <v>135321660</v>
       </c>
       <c r="B92" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11560,7 +11560,7 @@
         <v>135321668</v>
       </c>
       <c r="B93" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11778,7 +11778,7 @@
         <v>135321663</v>
       </c>
       <c r="B95" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11894,7 +11894,7 @@
         <v>135321665</v>
       </c>
       <c r="B96" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12010,7 +12010,7 @@
         <v>135325374</v>
       </c>
       <c r="B97" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12126,7 +12126,7 @@
         <v>135325376</v>
       </c>
       <c r="B98" t="n">
-        <v>80492</v>
+        <v>80530</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12242,7 +12242,7 @@
         <v>135321671</v>
       </c>
       <c r="B99" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12368,7 +12368,7 @@
         <v>135321672</v>
       </c>
       <c r="B100" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12494,7 +12494,7 @@
         <v>135323090</v>
       </c>
       <c r="B101" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12623,7 +12623,7 @@
         <v>135323092</v>
       </c>
       <c r="B102" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>135325377</v>
       </c>
       <c r="B103" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12868,7 +12868,7 @@
         <v>135325378</v>
       </c>
       <c r="B104" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12997,7 +12997,7 @@
         <v>135326036</v>
       </c>
       <c r="B105" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13122,7 +13122,7 @@
         <v>135321667</v>
       </c>
       <c r="B106" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13243,7 +13243,7 @@
         <v>135321669</v>
       </c>
       <c r="B107" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13364,7 +13364,7 @@
         <v>135321658</v>
       </c>
       <c r="B108" t="n">
-        <v>107695</v>
+        <v>107750</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13582,7 +13582,7 @@
         <v>135323095</v>
       </c>
       <c r="B110" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13698,7 +13698,7 @@
         <v>135321662</v>
       </c>
       <c r="B111" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13819,7 +13819,7 @@
         <v>135321664</v>
       </c>
       <c r="B112" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13940,7 +13940,7 @@
         <v>135321670</v>
       </c>
       <c r="B113" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14061,7 +14061,7 @@
         <v>135323089</v>
       </c>
       <c r="B114" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14177,7 +14177,7 @@
         <v>135323093</v>
       </c>
       <c r="B115" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14400,7 +14400,7 @@
         <v>135325384</v>
       </c>
       <c r="B117" t="n">
-        <v>92220</v>
+        <v>92262</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -15944,7 +15944,7 @@
         <v>135325383</v>
       </c>
       <c r="B132" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -18016,7 +18016,7 @@
         <v>135321675</v>
       </c>
       <c r="B152" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18132,7 +18132,7 @@
         <v>135325385</v>
       </c>
       <c r="B153" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>135326030</v>
       </c>
       <c r="B158" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18901,7 +18901,7 @@
         <v>135321676</v>
       </c>
       <c r="B160" t="n">
-        <v>57165</v>
+        <v>57170</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -20160,7 +20160,7 @@
         <v>135321674</v>
       </c>
       <c r="B172" t="n">
-        <v>92370</v>
+        <v>92412</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20291,7 +20291,7 @@
         <v>135325382</v>
       </c>
       <c r="B173" t="n">
-        <v>92370</v>
+        <v>92412</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20611,7 +20611,7 @@
         <v>135379346</v>
       </c>
       <c r="B176" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20829,7 +20829,7 @@
         <v>135321673</v>
       </c>
       <c r="B178" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20945,7 +20945,7 @@
         <v>135379343</v>
       </c>
       <c r="B179" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21061,7 +21061,7 @@
         <v>135325381</v>
       </c>
       <c r="B180" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21190,7 +21190,7 @@
         <v>135326032</v>
       </c>
       <c r="B181" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21528,7 +21528,7 @@
         <v>135325379</v>
       </c>
       <c r="B184" t="n">
-        <v>92661</v>
+        <v>92703</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21653,7 +21653,7 @@
         <v>135379344</v>
       </c>
       <c r="B185" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21769,7 +21769,7 @@
         <v>135379345</v>
       </c>
       <c r="B186" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>

--- a/artfynd/Maskaure Siebdniesjávrrie-Lillberget, 122 ha artfynd.xlsx
+++ b/artfynd/Maskaure Siebdniesjávrrie-Lillberget, 122 ha artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135323678</v>
       </c>
       <c r="B2" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>135379336</v>
       </c>
       <c r="B3" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>135323656</v>
       </c>
       <c r="B4" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>135323657</v>
       </c>
       <c r="B5" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>135321654</v>
       </c>
       <c r="B10" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>135323087</v>
       </c>
       <c r="B11" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>135325359</v>
       </c>
       <c r="B12" t="n">
-        <v>91966</v>
+        <v>91993</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>135325368</v>
       </c>
       <c r="B13" t="n">
-        <v>91966</v>
+        <v>91993</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>135379319</v>
       </c>
       <c r="B14" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>135325365</v>
       </c>
       <c r="B15" t="n">
-        <v>89396</v>
+        <v>89423</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>135323653</v>
       </c>
       <c r="B16" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>135325357</v>
       </c>
       <c r="B17" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>135325364</v>
       </c>
       <c r="B18" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>135379316</v>
       </c>
       <c r="B19" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>135379331</v>
       </c>
       <c r="B20" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         <v>135379317</v>
       </c>
       <c r="B21" t="n">
-        <v>81393</v>
+        <v>81420</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>135379320</v>
       </c>
       <c r="B22" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         <v>135323652</v>
       </c>
       <c r="B23" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>135325354</v>
       </c>
       <c r="B24" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>135325356</v>
       </c>
       <c r="B25" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>135325369</v>
       </c>
       <c r="B26" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>135379315</v>
       </c>
       <c r="B27" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
         <v>135379335</v>
       </c>
       <c r="B28" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>135379330</v>
       </c>
       <c r="B29" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>135379322</v>
       </c>
       <c r="B30" t="n">
-        <v>92371</v>
+        <v>92398</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>135325370</v>
       </c>
       <c r="B31" t="n">
-        <v>92362</v>
+        <v>92389</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>135321631</v>
       </c>
       <c r="B32" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>135321634</v>
       </c>
       <c r="B33" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         <v>135321636</v>
       </c>
       <c r="B34" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>135321640</v>
       </c>
       <c r="B35" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>135321650</v>
       </c>
       <c r="B36" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>135323672</v>
       </c>
       <c r="B37" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
         <v>135323673</v>
       </c>
       <c r="B38" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>135326033</v>
       </c>
       <c r="B39" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>135379323</v>
       </c>
       <c r="B40" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5315,7 +5315,7 @@
         <v>135379334</v>
       </c>
       <c r="B41" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         <v>135321635</v>
       </c>
       <c r="B42" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5547,7 +5547,7 @@
         <v>135321645</v>
       </c>
       <c r="B43" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
         <v>135321646</v>
       </c>
       <c r="B44" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5779,7 +5779,7 @@
         <v>135321651</v>
       </c>
       <c r="B45" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5895,7 +5895,7 @@
         <v>135379321</v>
       </c>
       <c r="B46" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6011,7 +6011,7 @@
         <v>135379324</v>
       </c>
       <c r="B47" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         <v>135379327</v>
       </c>
       <c r="B48" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6243,7 +6243,7 @@
         <v>135379333</v>
       </c>
       <c r="B49" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         <v>135379318</v>
       </c>
       <c r="B50" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -9494,7 +9494,7 @@
         <v>135321637</v>
       </c>
       <c r="B75" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9615,7 +9615,7 @@
         <v>135323085</v>
       </c>
       <c r="B76" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9731,7 +9731,7 @@
         <v>135379325</v>
       </c>
       <c r="B77" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9847,7 +9847,7 @@
         <v>135324140</v>
       </c>
       <c r="B78" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         <v>135326029</v>
       </c>
       <c r="B79" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10094,7 +10094,7 @@
         <v>135379341</v>
       </c>
       <c r="B80" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10646,7 +10646,7 @@
         <v>135323088</v>
       </c>
       <c r="B85" t="n">
-        <v>97352</v>
+        <v>97379</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10864,7 +10864,7 @@
         <v>135321659</v>
       </c>
       <c r="B87" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
         <v>135321666</v>
       </c>
       <c r="B88" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11096,7 +11096,7 @@
         <v>135323658</v>
       </c>
       <c r="B89" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11212,7 +11212,7 @@
         <v>135379339</v>
       </c>
       <c r="B90" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11328,7 +11328,7 @@
         <v>135379340</v>
       </c>
       <c r="B91" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11444,7 +11444,7 @@
         <v>135321660</v>
       </c>
       <c r="B92" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11560,7 +11560,7 @@
         <v>135321668</v>
       </c>
       <c r="B93" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11778,7 +11778,7 @@
         <v>135321663</v>
       </c>
       <c r="B95" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11894,7 +11894,7 @@
         <v>135321665</v>
       </c>
       <c r="B96" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12010,7 +12010,7 @@
         <v>135325374</v>
       </c>
       <c r="B97" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12126,7 +12126,7 @@
         <v>135325376</v>
       </c>
       <c r="B98" t="n">
-        <v>80530</v>
+        <v>80557</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -13122,7 +13122,7 @@
         <v>135321667</v>
       </c>
       <c r="B106" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13243,7 +13243,7 @@
         <v>135321669</v>
       </c>
       <c r="B107" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13364,7 +13364,7 @@
         <v>135321658</v>
       </c>
       <c r="B108" t="n">
-        <v>107750</v>
+        <v>107777</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13582,7 +13582,7 @@
         <v>135323095</v>
       </c>
       <c r="B110" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13698,7 +13698,7 @@
         <v>135321662</v>
       </c>
       <c r="B111" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13819,7 +13819,7 @@
         <v>135321664</v>
       </c>
       <c r="B112" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13940,7 +13940,7 @@
         <v>135321670</v>
       </c>
       <c r="B113" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14061,7 +14061,7 @@
         <v>135323089</v>
       </c>
       <c r="B114" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14177,7 +14177,7 @@
         <v>135323093</v>
       </c>
       <c r="B115" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14400,7 +14400,7 @@
         <v>135325384</v>
       </c>
       <c r="B117" t="n">
-        <v>92262</v>
+        <v>92289</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -15944,7 +15944,7 @@
         <v>135325383</v>
       </c>
       <c r="B132" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -18016,7 +18016,7 @@
         <v>135321675</v>
       </c>
       <c r="B152" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18132,7 +18132,7 @@
         <v>135325385</v>
       </c>
       <c r="B153" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -20160,7 +20160,7 @@
         <v>135321674</v>
       </c>
       <c r="B172" t="n">
-        <v>92412</v>
+        <v>92439</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20291,7 +20291,7 @@
         <v>135325382</v>
       </c>
       <c r="B173" t="n">
-        <v>92412</v>
+        <v>92439</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20611,7 +20611,7 @@
         <v>135379346</v>
       </c>
       <c r="B176" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20829,7 +20829,7 @@
         <v>135321673</v>
       </c>
       <c r="B178" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20945,7 +20945,7 @@
         <v>135379343</v>
       </c>
       <c r="B179" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21528,7 +21528,7 @@
         <v>135325379</v>
       </c>
       <c r="B184" t="n">
-        <v>92703</v>
+        <v>92730</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21653,7 +21653,7 @@
         <v>135379344</v>
       </c>
       <c r="B185" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21769,7 +21769,7 @@
         <v>135379345</v>
       </c>
       <c r="B186" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>

--- a/artfynd/Maskaure Siebdniesjávrrie-Lillberget, 122 ha artfynd.xlsx
+++ b/artfynd/Maskaure Siebdniesjávrrie-Lillberget, 122 ha artfynd.xlsx
@@ -13103,7 +13103,7 @@
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand, Anton Lundberg</t>
+          <t>Anton Lundberg, Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">

--- a/artfynd/Maskaure Siebdniesjávrrie-Lillberget, 122 ha artfynd.xlsx
+++ b/artfynd/Maskaure Siebdniesjávrrie-Lillberget, 122 ha artfynd.xlsx
@@ -13103,7 +13103,7 @@
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Anton Lundberg, Alva Dahlqvist Cederstrand</t>
+          <t>Alva Dahlqvist Cederstrand, Anton Lundberg</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">

--- a/artfynd/Maskaure Siebdniesjávrrie-Lillberget, 122 ha artfynd.xlsx
+++ b/artfynd/Maskaure Siebdniesjávrrie-Lillberget, 122 ha artfynd.xlsx
@@ -1675,7 +1675,7 @@
         <v>135321654</v>
       </c>
       <c r="B10" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>135325359</v>
       </c>
       <c r="B12" t="n">
-        <v>91998</v>
+        <v>92000</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>135325368</v>
       </c>
       <c r="B13" t="n">
-        <v>91998</v>
+        <v>92000</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>135325365</v>
       </c>
       <c r="B15" t="n">
-        <v>89426</v>
+        <v>89428</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>135323653</v>
       </c>
       <c r="B16" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>135325357</v>
       </c>
       <c r="B17" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>135325364</v>
       </c>
       <c r="B18" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>135379316</v>
       </c>
       <c r="B19" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>135379331</v>
       </c>
       <c r="B20" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>135379320</v>
       </c>
       <c r="B22" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         <v>135323652</v>
       </c>
       <c r="B23" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>135325354</v>
       </c>
       <c r="B24" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>135325356</v>
       </c>
       <c r="B25" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>135325369</v>
       </c>
       <c r="B26" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>135379315</v>
       </c>
       <c r="B27" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
         <v>135379335</v>
       </c>
       <c r="B28" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>135379322</v>
       </c>
       <c r="B30" t="n">
-        <v>92403</v>
+        <v>92405</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>135325370</v>
       </c>
       <c r="B31" t="n">
-        <v>92394</v>
+        <v>92396</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -9494,7 +9494,7 @@
         <v>135321637</v>
       </c>
       <c r="B75" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9615,7 +9615,7 @@
         <v>135323085</v>
       </c>
       <c r="B76" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10646,7 +10646,7 @@
         <v>135323088</v>
       </c>
       <c r="B85" t="n">
-        <v>97384</v>
+        <v>97386</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -13122,7 +13122,7 @@
         <v>135321667</v>
       </c>
       <c r="B106" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13243,7 +13243,7 @@
         <v>135321669</v>
       </c>
       <c r="B107" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13364,7 +13364,7 @@
         <v>135321658</v>
       </c>
       <c r="B108" t="n">
-        <v>107782</v>
+        <v>107784</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13582,7 +13582,7 @@
         <v>135323095</v>
       </c>
       <c r="B110" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13698,7 +13698,7 @@
         <v>135321662</v>
       </c>
       <c r="B111" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13819,7 +13819,7 @@
         <v>135321664</v>
       </c>
       <c r="B112" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13940,7 +13940,7 @@
         <v>135321670</v>
       </c>
       <c r="B113" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14061,7 +14061,7 @@
         <v>135323089</v>
       </c>
       <c r="B114" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14177,7 +14177,7 @@
         <v>135323093</v>
       </c>
       <c r="B115" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14400,7 +14400,7 @@
         <v>135325384</v>
       </c>
       <c r="B117" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -15944,7 +15944,7 @@
         <v>135325383</v>
       </c>
       <c r="B132" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -20160,7 +20160,7 @@
         <v>135321674</v>
       </c>
       <c r="B172" t="n">
-        <v>92444</v>
+        <v>92446</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20291,7 +20291,7 @@
         <v>135325382</v>
       </c>
       <c r="B173" t="n">
-        <v>92444</v>
+        <v>92446</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -21528,7 +21528,7 @@
         <v>135325379</v>
       </c>
       <c r="B184" t="n">
-        <v>92735</v>
+        <v>92737</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>

--- a/artfynd/Maskaure Siebdniesjávrrie-Lillberget, 122 ha artfynd.xlsx
+++ b/artfynd/Maskaure Siebdniesjávrrie-Lillberget, 122 ha artfynd.xlsx
@@ -8243,7 +8243,7 @@
         <v>135325358</v>
       </c>
       <c r="B65" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
         <v>135325360</v>
       </c>
       <c r="B66" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -21061,7 +21061,7 @@
         <v>135325381</v>
       </c>
       <c r="B180" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
